--- a/artfynd/A 2424-2022 artfynd.xlsx
+++ b/artfynd/A 2424-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2424-2022 artfynd.xlsx
+++ b/artfynd/A 2424-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62082645</v>
+        <v>17127324</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Knaben</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örberga 9850/4550, Nrk</t>
+          <t>Örberga, 600 m VNV om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500856.0589848422</v>
+        <v>500830</v>
       </c>
       <c r="R2" t="n">
-        <v>6537595.52036513</v>
+        <v>6537548</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +738,24 @@
           <t>Lerbäck</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>T-Ask-2779-biogeo</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-05-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1960-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1960-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hallin ms.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>62362051</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500856.0589848422</v>
+        <v>500856</v>
       </c>
       <c r="R3" t="n">
-        <v>6537595.52036513</v>
+        <v>6537596</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +854,9 @@
           <t>1960-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1960-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,12 +891,7 @@
         <v>62536645</v>
       </c>
       <c r="B4" t="n">
-        <v>101128</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500856.062314478</v>
+        <v>500856</v>
       </c>
       <c r="R4" t="n">
-        <v>6537580.570540617</v>
+        <v>6537581</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,19 +960,9 @@
           <t>1981-05-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1981-05-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1025,62 +994,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62732897</v>
+        <v>77455001</v>
       </c>
       <c r="B5" t="n">
-        <v>103430</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224210</v>
+        <v>222009</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örberga 9850/4550, Nrk</t>
+          <t>Örberga 9835/4539, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500856.062314478</v>
+        <v>500845</v>
       </c>
       <c r="R5" t="n">
-        <v>6537580.570540617</v>
+        <v>6537581</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,27 +1068,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1981-04-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1981-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 16 vinterståndare, 20 m S vägen</t>
+          <t>Urkalkhäll. 7 blommor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,11 +1089,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Urkalk under kraftledning</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,6 +1102,450 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95186821</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Luckebo 9872/4544, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500850</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6537618</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ganska rikligt i norra vägrenen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>62082635</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örberga 9850/4550, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500856</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6537596</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1960-12-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkberg 7</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3863817</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örberga, VNV om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500844</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6537587</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>T-Ask-0530</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2003-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2003-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Området ligger i en kraftledningsgata i bergsluttningen omedelbart söder om vägen mot Luckebo. Ledningsgatan är bevuxen med täta grupper av enar. Mellan dessa finns mindre gläntor, där jordtäcket är tunnare. En långsträckt, ca 3-5 m bred glänta med en mycket otydlig stig finns under ledningens mittlina. Ca 30 m från vägen ansluter, med en smal mynning, wn oval (ca 4 x 15 m) tvärglänta åt öster. I gläntan och ledningsgatan finns talrika små hällytor utkalk. Arten växer både i tvärgläntan och i anslutande del av ledningsgatan. Från rakt under ledningens mittlina når beståndet ca 9 m in i gläntan och i ledningsgatan sträcker sträcker det sig från ca 2 m ovanför (S om) till ca 8 m nedanför (N om) tvärgläntans mynning. Föregående år sågs enstaka plantor även några meter längre ner i ledningsgatan. I gläntan sågs ca 60 och i ledningsgatan 25 plantor.Motsvarande siffror förra året var ca 32 och 13. Plantorna växer i huvudsak på det tunna jordtäcket intill hällytorna.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Klippäng</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>62732896</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örberga 9850/4550, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500856</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6537581</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1981-07-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1981-07-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 ex i tidig blom</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2424-2022 artfynd.xlsx
+++ b/artfynd/A 2424-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17127324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62362051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62536645</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77455001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95186821</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3863817</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,8 +1586,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62732896</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>